--- a/docs/files/REPORT_FILTRI/Agente - CR ROMANO CARMELA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR ROMANO CARMELA.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - CR ROMANO CARMELA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR ROMANO CARMELA.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -859,14 +859,14 @@
         <v>0</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - CR ROMANO CARMELA.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - CR ROMANO CARMELA.xlsx
@@ -538,7 +538,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>1</v>
@@ -850,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
